--- a/Result/profitability/4303.xlsx
+++ b/Result/profitability/4303.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.03125</v>
+        <v>2.21625</v>
       </c>
       <c r="N2" t="n">
-        <v>16.1675</v>
+        <v>16.78</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.23</v>
       </c>
       <c r="M3" t="n">
-        <v>2.2175</v>
+        <v>1.38875</v>
       </c>
       <c r="N3" t="n">
-        <v>15.80875</v>
+        <v>17.21875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>-0.63</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2825</v>
+        <v>0.3662500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>14.47375</v>
+        <v>15.49625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3687500000000001</v>
+        <v>1.14125</v>
       </c>
       <c r="N5" t="n">
-        <v>13.6725</v>
+        <v>13.70375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07125</v>
+        <v>0.02625000000000028</v>
       </c>
       <c r="N6" t="n">
-        <v>11.7</v>
+        <v>11.98375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1268,10 +1268,10 @@
         <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02375000000000022</v>
+        <v>-0.06999999999999973</v>
       </c>
       <c r="N7" t="n">
-        <v>12.0525</v>
+        <v>12.17</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1395,10 +1395,10 @@
         <v>0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07624999999999978</v>
+        <v>0.01125000000000028</v>
       </c>
       <c r="N8" t="n">
-        <v>10.755</v>
+        <v>10.88625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00125000000000022</v>
+        <v>0.001250000000000279</v>
       </c>
       <c r="N9" t="n">
         <v>10.69375</v>
@@ -1649,7 +1649,7 @@
         <v>-0.15</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01749999999999978</v>
+        <v>-0.01749999999999972</v>
       </c>
       <c r="N10" t="n">
         <v>9.963750000000001</v>
@@ -1776,7 +1776,7 @@
         <v>0.23</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01749999999999978</v>
+        <v>-0.01749999999999972</v>
       </c>
       <c r="N11" t="n">
         <v>10.60125</v>
@@ -1903,7 +1903,7 @@
         <v>-0.29</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02500000000000022</v>
+        <v>0.02500000000000028</v>
       </c>
       <c r="N12" t="n">
         <v>12.585</v>
@@ -2030,7 +2030,7 @@
         <v>-0.11</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.01874999999999977</v>
+        <v>-0.01874999999999972</v>
       </c>
       <c r="N13" t="n">
         <v>11.36</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>287</v>
+      </c>
+      <c r="D75" t="n">
+        <v>228</v>
+      </c>
+      <c r="E75" t="n">
+        <v>59</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.34%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>75</v>
+      </c>
+      <c r="J75" t="n">
+        <v>74</v>
+      </c>
+      <c r="K75" t="n">
+        <v>20</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.05875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.97125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.458333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.049999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05376344086021501</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.036912751677852</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01229709788489908</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
